--- a/labelled_comments.xlsx
+++ b/labelled_comments.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitar\Documents\side hustles\pragmatis\sentiment analysis\instagram\1\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitar\Documents\side hustles\pragmatis\sentiment analysis\instagram\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34E79417-5085-429C-9A22-5AEDA810DB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD4C1803-059C-4113-BC2F-3608CDC96F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="101">
   <si>
     <t>username</t>
   </si>
@@ -41,293 +28,302 @@
     <t>comment</t>
   </si>
   <si>
-    <t>dinar_candy</t>
-  </si>
-  <si>
-    <t>Gemoy team 🙌🙌🙌🙌</t>
-  </si>
-  <si>
-    <t>rositaputri_04</t>
-  </si>
-  <si>
-    <t>Kalo soal pa Prabowo pasti saya like ❤️</t>
-  </si>
-  <si>
-    <t>williamkaunang</t>
-  </si>
-  <si>
-    <t>TUAMA 🔥
-Prabowo Presiden 2024 🇮🇩</t>
-  </si>
-  <si>
-    <t>muhammaddedieee</t>
-  </si>
-  <si>
-    <t>@muhammaddedieee jadi pawang angin 💨😂</t>
-  </si>
-  <si>
-    <t>bunda_jannah</t>
-  </si>
-  <si>
-    <t>All in prabowo gibran ❤️❤️</t>
-  </si>
-  <si>
-    <t>imelnra</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na gagasan tok gaonok aksine, nggedabrusss. Wareg ta mangan gagasan?🤣</t>
+    <t>prczalt</t>
+  </si>
+  <si>
+    <t>Absen yang All pak Bowo dan mas Gibran---------&gt;</t>
+  </si>
+  <si>
+    <t>visit_kalsel_new</t>
+  </si>
+  <si>
+    <t>Para artis dan selebgram dukung 02 utk kelancaran bisnisnya dan kemakmuran para pejabat , elite politik ❎
+Kita dukung 01 utk kesejahteraan dan kemakmuran rakyat , serta keadilan sosial bagi seluruh rakyat Indonesia ✅</t>
+  </si>
+  <si>
+    <t>salenduyuni</t>
+  </si>
+  <si>
+    <t>All in Prabowo...02 pasti MENANG🔥🔥🔥</t>
+  </si>
+  <si>
+    <t>muhamadrizki25063</t>
+  </si>
+  <si>
+    <t>Soryy yehhh #01MENANG UNTUK PERUBAHAN</t>
+  </si>
+  <si>
+    <t>cesaryuga</t>
+  </si>
+  <si>
+    <t>BNGGA DG ARTIS MUDA INDONESI 💙✌🏻🔥</t>
+  </si>
+  <si>
+    <t>andri_j77</t>
+  </si>
+  <si>
+    <t>Pendukung sebelah makin panas😂😂</t>
+  </si>
+  <si>
+    <t>muh_nurharis</t>
+  </si>
+  <si>
+    <t>01 Anis☝</t>
+  </si>
+  <si>
+    <t>eliandri_bahtiar</t>
+  </si>
+  <si>
+    <t>Padahal masih user MELON ELPIJI, tapi malah dukung pejabat NAIK GAJI!!!</t>
+  </si>
+  <si>
+    <t>jimi70tv</t>
+  </si>
+  <si>
+    <t>Tombol all in Prabowo Gibran 💙💙 -----&gt;&gt;</t>
+  </si>
+  <si>
+    <t>achidddd</t>
+  </si>
+  <si>
+    <t>tuama bkg manado bergetar😍😍🔥🔥🔥👏👏✌️✌️✌️</t>
+  </si>
+  <si>
+    <t>ap16___</t>
+  </si>
+  <si>
+    <t>ada kepentingan pribadi apaan kira” dukung yg banyak yg bermasalah fer?</t>
+  </si>
+  <si>
+    <t>aku_nanag3</t>
+  </si>
+  <si>
+    <t>01❤️</t>
+  </si>
+  <si>
+    <t>anry.sumarna</t>
+  </si>
+  <si>
+    <t>Saya 2 kali pilih bapak, skrg waktunya istirahat pak 😢😢 #01 ☝🏻</t>
+  </si>
+  <si>
+    <t>malanur_20</t>
+  </si>
+  <si>
+    <t>screenshot komen gw bang gw yakin dukung 02 all in presiden 2024✌️💙</t>
+  </si>
+  <si>
+    <t>a.g_pratama</t>
+  </si>
+  <si>
+    <t>01🔥🔥❤️</t>
+  </si>
+  <si>
+    <t>addy_900444</t>
+  </si>
+  <si>
+    <t>Tetap NOMOR 1 ☝☝☝☝☝☝☝☝☝☝☝☝☝☝☝☝❤❤❤❤❤❤😎😎😎😎😎😎</t>
   </si>
   <si>
     <t>annetteldewi</t>
   </si>
   <si>
-    <t>Terbaikk memang Bapak Prabowo!🔥🔥</t>
-  </si>
-  <si>
-    <t>smartlivingwithnasar</t>
-  </si>
-  <si>
-    <t>All in PrabowoGibran ✌🏻</t>
-  </si>
-  <si>
-    <t>deayuanggi</t>
-  </si>
-  <si>
-    <t>Garis keras Prabowo ni tampaknya bg😂</t>
-  </si>
-  <si>
-    <t>Aku semakin yakin dukung anis imin</t>
-  </si>
-  <si>
-    <t>mamaeyuti</t>
-  </si>
-  <si>
-    <t>All in prabowo gibran 😍😍</t>
-  </si>
-  <si>
-    <t>ddsfit3</t>
-  </si>
-  <si>
-    <t>BUAH SAWO DI MAKAN LURAH,GUA MAH PRABOWO LU MAH TERSERAH 🔥</t>
-  </si>
-  <si>
-    <t>see_frzzzzzzz</t>
-  </si>
-  <si>
-    <t>Pantaskah seorang yg mencintaipi kekayaan seseorang kemudian menyinyirinya dan enggan berterima kasih? Pantaskah dia berbicara soal etik?? Pantaskah dia bicara soal pesawat bekas, pak Prabowo memesan yg bekas untuk menutupi kekosongan karna sebagian pesawat udah pensiun, memsan yg baru itu datangnya tidak singkat, itu membutuhkan waktu yg lama bertahun" pantaskah membeberkan rahasia negara ditempat umum?? PANTASKAH?? ingat mass, percuma ijazah setinggi langit dan penghargaan segunung kalau atitud gk ada, banyak yg bilang pak Prabowo berambisi jadi presiden karena gagal 2 kali, tapi untuk malam ini membuktikan anislah yg sangat berambisi, sakit banget gk sih dikhianati lalu dicecar , sy aja yg menyaksikan syg sakit hati , bagaimana jika yg merasakan, sy akui dari dulu sy sgt suka dgn pak anis sy respect dan senang dgn pak anis, tapi untuk saat ini sy akui kalau dulu sy pernah bodoh menilai seseorang, TERIMAKASIH.!!</t>
-  </si>
-  <si>
-    <t>mia.adrianna__</t>
-  </si>
-  <si>
-    <t>Sehat selalu Pak Prabowo dan bang Fero😊🥰😍♥️</t>
-  </si>
-  <si>
-    <t>umamilidya</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na janji2 tok nyatane ndopok😂😂</t>
-  </si>
-  <si>
-    <t>stifvibes</t>
-  </si>
-  <si>
-    <t>Putra Minahasa ✌🏻</t>
-  </si>
-  <si>
-    <t>andika_prasetia</t>
-  </si>
-  <si>
-    <t>Jendral Prabowo 🔥🔥🔥🔥</t>
-  </si>
-  <si>
-    <t>arya_sampoerna</t>
-  </si>
-  <si>
-    <t>Badokan tok kurang gagasan</t>
-  </si>
-  <si>
-    <t>ekomulyadii</t>
-  </si>
-  <si>
-    <t>Mantap abang Fero 👍🏻👍🏻👍🏻</t>
-  </si>
-  <si>
-    <t>deby_prnmsr512</t>
-  </si>
-  <si>
-    <t>Bismillah prabowo gibran🤲</t>
-  </si>
-  <si>
-    <t>m.sofyan_s.ml</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na banyak gagasan,banyak teori bisanya cuman gelapin uang rakyat itu yng di dukung,memang zaman udh kebalik ya skarang😂</t>
-  </si>
-  <si>
-    <t>dizzyy_mntlng</t>
-  </si>
-  <si>
-    <t>TORANG DG TUAMA🔥🔥</t>
-  </si>
-  <si>
-    <t>dinarwahyu_akunbaru</t>
-  </si>
-  <si>
-    <t>All in🔥</t>
-  </si>
-  <si>
-    <t>adya_llss</t>
-  </si>
-  <si>
-    <t>Bingun sama artis artis mereka padahal rata rata berpendidikan tinggi.. Tapi apa buta mata buta hati banyak dukung paslon yang punya wakil jalur MK dan curang 😢</t>
-  </si>
-  <si>
-    <t>sri_damayanti_022</t>
-  </si>
-  <si>
-    <t>Dikampung aku ka😍seneng bgt bisa ketemu ka Fero langsung😍❤️</t>
-  </si>
-  <si>
-    <t>All in prabowo gibran😍😍😍😍</t>
-  </si>
-  <si>
-    <t>ridwanalvaro_12</t>
-  </si>
-  <si>
-    <t>Keren lu bang 🔥👏</t>
-  </si>
-  <si>
-    <t>vickymci7</t>
-  </si>
-  <si>
-    <t>@fero_walandouw Mantapss 🔥🔥 Terbaik Pak Prabowo 👍😇🙏✌️</t>
-  </si>
-  <si>
-    <t>doddyansyah</t>
-  </si>
-  <si>
-    <t>👏</t>
-  </si>
-  <si>
-    <t>zarhendrik</t>
-  </si>
-  <si>
-    <t>✌🏻✌🏻✌🏻</t>
-  </si>
-  <si>
-    <t>junior_trimunanda</t>
-  </si>
-  <si>
-    <t>ALL IN PRABOWO ✌️🔥</t>
-  </si>
-  <si>
-    <t>aniezaniz2</t>
-  </si>
-  <si>
-    <t>✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️</t>
-  </si>
-  <si>
-    <t>tatimandaaa</t>
-  </si>
-  <si>
-    <t>Makin Mantap Pilih nomer 2 All in Prabowo Loveeeee❤️❤️❤️❤️❤️❤️❤️</t>
-  </si>
-  <si>
-    <t>sulasmita</t>
-  </si>
-  <si>
-    <t>Pak gemoy😍❤️❤️❤️</t>
-  </si>
-  <si>
-    <t>secrettmeong_</t>
-  </si>
-  <si>
-    <t>Yang pendukung @prabowo rata2 kenapa berkelas semua ya❤️</t>
-  </si>
-  <si>
-    <t>askom1805</t>
-  </si>
-  <si>
-    <t>Mantap abang ku✌️💙</t>
-  </si>
-  <si>
-    <t>kevinzethizac</t>
-  </si>
-  <si>
-    <t>maju AMIN !!!🔥</t>
-  </si>
-  <si>
-    <t>miftahul448jannah</t>
-  </si>
-  <si>
-    <t>Kereeen 👌 bang fero</t>
-  </si>
-  <si>
-    <t>sabryan_macca</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na buzzer</t>
-  </si>
-  <si>
-    <t>sam_rajiemin54</t>
-  </si>
-  <si>
-    <t>Pantesan jadi Komisaris😂</t>
-  </si>
-  <si>
-    <t>ajayfalikan</t>
-  </si>
-  <si>
-    <t>Hidup pak Prabowo</t>
-  </si>
-  <si>
-    <t>ghofir04</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na gagasannya internet gratis buat mbokep 😂😂😂</t>
-  </si>
-  <si>
-    <t>syarifsyarif4752</t>
-  </si>
-  <si>
-    <t>@see_frzzzzzzz 2kali Prabowo nyapres gak pernah gue milih beliau.. beliau terlalu arogan.. tp setelah diya mau jadi pembantunya Jokowi,,aku malah respect ma pak Wowo.. ternyata setulus tu cintanya kepada Indonesia</t>
-  </si>
-  <si>
-    <t>sriyatun_2375</t>
-  </si>
-  <si>
-    <t>Mantap bang Fero aku mendukung Paslon Abang 👍💪❤️</t>
-  </si>
-  <si>
-    <t>bebyila02</t>
-  </si>
-  <si>
-    <t>@adya_llss itu hak mbak, terserah pilih siapa</t>
-  </si>
-  <si>
-    <t>isnainihayati11</t>
-  </si>
-  <si>
-    <t>Jejak digital .... selamat jadi komisaris😂</t>
-  </si>
-  <si>
-    <t>st_efany8178</t>
-  </si>
-  <si>
-    <t>Prabowo gibran❤️</t>
-  </si>
-  <si>
-    <t>lokeramboncom</t>
-  </si>
-  <si>
-    <t>Jika hanya ada 1 suara di Ambon dalam Pemilihan nanti. Maka itulah Saya Pak @prabowo ✌️</t>
-  </si>
-  <si>
-    <t>poyluccc</t>
-  </si>
-  <si>
-    <t>dapet apa sih??? udh gak laku ya sinetronnya?</t>
+    <t>Menado SEBIRU LANGIT YANG INDAH dengan Bapak @prabowo DATANG!!!🩵🩵🩵🩵🩵</t>
+  </si>
+  <si>
+    <t>vicky_alycia_fitri</t>
+  </si>
+  <si>
+    <t>Masa allah😢😢 absen kak taiwan taipe 02🔥❤️❤️✌️✌️</t>
+  </si>
+  <si>
+    <t>aliya_formosagirl</t>
+  </si>
+  <si>
+    <t>😍😍😍love you bapak 😍</t>
+  </si>
+  <si>
+    <t>ninink0505</t>
+  </si>
+  <si>
+    <t>@ap16___ yg bermasalah itu mulut lu mas</t>
+  </si>
+  <si>
+    <t>navindiarii</t>
+  </si>
+  <si>
+    <t>@ap16___ lu ngapa?</t>
+  </si>
+  <si>
+    <t>kholisnawawi06</t>
+  </si>
+  <si>
+    <t>TETAP NOMOR 1 ANIS MUHAIMIN❤️</t>
+  </si>
+  <si>
+    <t>denicandra160499</t>
+  </si>
+  <si>
+    <t>📌 14 0️⃣2️⃣ 2024 Oke Gas Dukungan kita kepada Prabowo-Gibran RI 1 🇲🇨 ==========++++&gt;</t>
+  </si>
+  <si>
+    <t>itscharmes</t>
+  </si>
+  <si>
+    <t>Di Manado ini??😍😍salam Gemooyy pak✌️❤️</t>
+  </si>
+  <si>
+    <t>@ap16___ pantes engga ada beda nya jari sama mulut sama² bermasalah</t>
+  </si>
+  <si>
+    <t>dindareyn</t>
+  </si>
+  <si>
+    <t>Masyaalloh sehat selalu pak Prabowo 😍😍</t>
+  </si>
+  <si>
+    <t>jeinmongs</t>
+  </si>
+  <si>
+    <t>Kage leh abis itu drg blg edit 😢 pdhl real real . tetap ALL IN GUYS</t>
+  </si>
+  <si>
+    <t>_paadddd</t>
+  </si>
+  <si>
+    <t>@visit_kalsel_new ciee kepanasan cieee</t>
+  </si>
+  <si>
+    <t>andri_frnnd</t>
+  </si>
+  <si>
+    <t>Rasulullah Saw telah menegaskan kepada kita ;
+"Barangsiapa yang mengangkat seseorang untuk suatu jabatan (sebagai pemimpin) yang berkaitan dengan urusan masyarakat sedangkan dia mengetahui ada yang lebih tepat, maka sesungguhnya ia telah mengkhianati Allah, Rasul dan kaum muslimin lainnya”. Sabda Nabi lainnya; “Bagaimana keadaan kalian, demikian pula ditetapkan oleh penguasa (pemimpin) atas kalian”. Pepatah Arab telah menegaskan bahwa; “Sebagaimana adanya dirimu, begitulah pemimpin yang akan memimpinmu”. Maknanya adalah; Pilihlah pemimpin yang tepat, jangan memilih pemimpin yang tidak atau belum layak/pantas untuk memimpin, apalagi memilih pemimpin yang maju dengan cara-cara melanggar hukum sementara pemimpin yang lebih layak/pantas justru kita abaikan, karena pemimpin itu ibarat cerminan dari masyarakatnya. Pemimpin yang baik adalah pemimpin yang dapat menangkap aspirasi masyarakatnya, sedangkan masyarakat yang baik adalah masyarakat yang berusaha mewujudkan pemimpin yang dapat menyalurkan aspirasi mereka”.
+*dikutip dari M. Quraish Shihab (1994) dalam bukunya “Lentera hati”</t>
+  </si>
+  <si>
+    <t>marusaha_siitumorang</t>
+  </si>
+  <si>
+    <t>Pendukung 02 yg bermasalah semua dgn hukum😂</t>
+  </si>
+  <si>
+    <t>misteriuz24</t>
+  </si>
+  <si>
+    <t>01 masih menyala boskuh🔥🔥🔥. 02 sorry yeee</t>
+  </si>
+  <si>
+    <t>marliaajah</t>
+  </si>
+  <si>
+    <t>Pokoknya dukung prabowo gibran gemoy</t>
+  </si>
+  <si>
+    <t>eggin_29</t>
+  </si>
+  <si>
+    <t>MANADO NIH BOSSS🥰🥰 ALL IN DENG PRABOWO ✌️ OKE GAS" NOMOR 2 TORANG GAS😇🙏</t>
+  </si>
+  <si>
+    <t>sumarni6673</t>
+  </si>
+  <si>
+    <t>Bismillah 🔥🔥✌️02 semangat ua untuk semunya</t>
+  </si>
+  <si>
+    <t>rusmaernaw</t>
+  </si>
+  <si>
+    <t>Salfok sama mayor teddy😍</t>
+  </si>
+  <si>
+    <t>nadioandrias_03</t>
+  </si>
+  <si>
+    <t>pilih lah pemimpin yg sehat</t>
+  </si>
+  <si>
+    <t>mikehope._</t>
+  </si>
+  <si>
+    <t>Kaseh biru Sulut ❄️❄️</t>
+  </si>
+  <si>
+    <t>ru.na5443</t>
+  </si>
+  <si>
+    <t>Sehat2 semuanya🔥🔥💙💙</t>
+  </si>
+  <si>
+    <t>14__putra</t>
+  </si>
+  <si>
+    <t>01 perubahan dong 🔥🔥</t>
+  </si>
+  <si>
+    <t>sugiharto_bonex</t>
+  </si>
+  <si>
+    <t>01... Amiin ❤️❤️</t>
+  </si>
+  <si>
+    <t>ambil_wuling_yuk</t>
+  </si>
+  <si>
+    <t>@andri_j77 ngapain panas toh yg pakai dana panas kan tim 02, kita mah 01 B aja 😂😂</t>
+  </si>
+  <si>
+    <t>rinindriyanii</t>
+  </si>
+  <si>
+    <t>@visit_kalsel_new 1. Buka Google
+2. Ketika Doa Penghilng iri hati dan dengki 3. Amalkan</t>
+  </si>
+  <si>
+    <t>zakia_nurhazanah</t>
+  </si>
+  <si>
+    <t>@ap16___ buzer panas terus😂</t>
+  </si>
+  <si>
+    <t>khdjaahrp_</t>
+  </si>
+  <si>
+    <t>Bismillah 2024 Pragib ❤️</t>
+  </si>
+  <si>
+    <t>@grafik.utama STOP REZIM STOP POLITIK DINASTI!!! HIDUP INDONESIA YG LEBIH UNGGUL 🔥🔥🔥</t>
+  </si>
+  <si>
+    <t>barryanggriawan</t>
+  </si>
+  <si>
+    <t>@andri_j77 baru kali ini kampanye eyang wowo rame😂 beda sama anies kemanapun selalu rame. Beda kelas bro😂</t>
+  </si>
+  <si>
+    <t>____nar.v</t>
+  </si>
+  <si>
+    <t>@andri_j77 kami kan masik waras, kalo sono cacat mk wkwkwk</t>
+  </si>
+  <si>
+    <t>doeabduh</t>
+  </si>
+  <si>
+    <t>Anies makin yakin gue</t>
+  </si>
+  <si>
+    <t>sakariaiyas</t>
+  </si>
+  <si>
+    <t>✌️🔥</t>
+  </si>
+  <si>
+    <t>grafis.tama</t>
+  </si>
+  <si>
+    <t>@eliandribachtiar ANAK MUDA GEN Z yg baca ini... BERBAKTILAH PADA ORG TUA KALIAN dgn tidak memberatkan Hidup dan biaya hidup mereka atas Ke FOMO dan Kebutaan kalian dalam memilih Pemimpin.... Kalian yg masih bergantung org tua, kalian yg belum berkeluarga pasti akan sulit merasakan betapa Sulit dan Mahalnya hidup, jika rezim ini di Lanjutkan</t>
   </si>
   <si>
     <t>sentiment_score</t>
@@ -699,11 +695,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="106.08984375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -714,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -724,11 +719,8 @@
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -736,10 +728,10 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -758,7 +750,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -772,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -780,7 +772,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -791,7 +783,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -802,7 +794,7 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -813,59 +805,59 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="232" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -873,32 +865,32 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -906,98 +898,98 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C25">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C26">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1005,54 +997,54 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="203" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1060,10 +1052,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1071,10 +1063,10 @@
     </row>
     <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1082,43 +1074,43 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1126,32 +1118,32 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C39">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C40">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>-1</v>
@@ -1159,60 +1151,60 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44">
         <v>-0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -1220,7 +1212,7 @@
         <v>91</v>
       </c>
       <c r="C47">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -1231,10 +1223,10 @@
         <v>93</v>
       </c>
       <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -1242,7 +1234,7 @@
         <v>95</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -1253,7 +1245,18 @@
         <v>97</v>
       </c>
       <c r="C50">
-        <v>-0.5</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/labelled_comments.xlsx
+++ b/labelled_comments.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitar\Documents\side hustles\pragmatis\sentiment analysis\instagram\1\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nitar\Documents\side hustles\pragmatis\sentiment analysis\instagram\4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34E79417-5085-429C-9A22-5AEDA810DB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C263A2D-BE48-4FFE-B736-6ABDF40C627D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
   <si>
     <t>username</t>
   </si>
@@ -41,293 +28,295 @@
     <t>comment</t>
   </si>
   <si>
-    <t>dinar_candy</t>
-  </si>
-  <si>
-    <t>Gemoy team 🙌🙌🙌🙌</t>
-  </si>
-  <si>
-    <t>rositaputri_04</t>
-  </si>
-  <si>
-    <t>Kalo soal pa Prabowo pasti saya like ❤️</t>
-  </si>
-  <si>
-    <t>williamkaunang</t>
-  </si>
-  <si>
-    <t>TUAMA 🔥
-Prabowo Presiden 2024 🇮🇩</t>
-  </si>
-  <si>
-    <t>muhammaddedieee</t>
-  </si>
-  <si>
-    <t>@muhammaddedieee jadi pawang angin 💨😂</t>
-  </si>
-  <si>
-    <t>bunda_jannah</t>
-  </si>
-  <si>
-    <t>All in prabowo gibran ❤️❤️</t>
-  </si>
-  <si>
-    <t>imelnra</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na gagasan tok gaonok aksine, nggedabrusss. Wareg ta mangan gagasan?🤣</t>
-  </si>
-  <si>
-    <t>annetteldewi</t>
-  </si>
-  <si>
-    <t>Terbaikk memang Bapak Prabowo!🔥🔥</t>
-  </si>
-  <si>
-    <t>smartlivingwithnasar</t>
-  </si>
-  <si>
-    <t>All in PrabowoGibran ✌🏻</t>
-  </si>
-  <si>
-    <t>deayuanggi</t>
-  </si>
-  <si>
-    <t>Garis keras Prabowo ni tampaknya bg😂</t>
-  </si>
-  <si>
-    <t>Aku semakin yakin dukung anis imin</t>
-  </si>
-  <si>
-    <t>mamaeyuti</t>
-  </si>
-  <si>
-    <t>All in prabowo gibran 😍😍</t>
-  </si>
-  <si>
-    <t>ddsfit3</t>
-  </si>
-  <si>
-    <t>BUAH SAWO DI MAKAN LURAH,GUA MAH PRABOWO LU MAH TERSERAH 🔥</t>
-  </si>
-  <si>
-    <t>see_frzzzzzzz</t>
-  </si>
-  <si>
-    <t>Pantaskah seorang yg mencintaipi kekayaan seseorang kemudian menyinyirinya dan enggan berterima kasih? Pantaskah dia berbicara soal etik?? Pantaskah dia bicara soal pesawat bekas, pak Prabowo memesan yg bekas untuk menutupi kekosongan karna sebagian pesawat udah pensiun, memsan yg baru itu datangnya tidak singkat, itu membutuhkan waktu yg lama bertahun" pantaskah membeberkan rahasia negara ditempat umum?? PANTASKAH?? ingat mass, percuma ijazah setinggi langit dan penghargaan segunung kalau atitud gk ada, banyak yg bilang pak Prabowo berambisi jadi presiden karena gagal 2 kali, tapi untuk malam ini membuktikan anislah yg sangat berambisi, sakit banget gk sih dikhianati lalu dicecar , sy aja yg menyaksikan syg sakit hati , bagaimana jika yg merasakan, sy akui dari dulu sy sgt suka dgn pak anis sy respect dan senang dgn pak anis, tapi untuk saat ini sy akui kalau dulu sy pernah bodoh menilai seseorang, TERIMAKASIH.!!</t>
-  </si>
-  <si>
-    <t>mia.adrianna__</t>
-  </si>
-  <si>
-    <t>Sehat selalu Pak Prabowo dan bang Fero😊🥰😍♥️</t>
-  </si>
-  <si>
-    <t>umamilidya</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na janji2 tok nyatane ndopok😂😂</t>
-  </si>
-  <si>
-    <t>stifvibes</t>
-  </si>
-  <si>
-    <t>Putra Minahasa ✌🏻</t>
-  </si>
-  <si>
-    <t>andika_prasetia</t>
-  </si>
-  <si>
-    <t>Jendral Prabowo 🔥🔥🔥🔥</t>
-  </si>
-  <si>
-    <t>arya_sampoerna</t>
-  </si>
-  <si>
-    <t>Badokan tok kurang gagasan</t>
-  </si>
-  <si>
-    <t>ekomulyadii</t>
-  </si>
-  <si>
-    <t>Mantap abang Fero 👍🏻👍🏻👍🏻</t>
-  </si>
-  <si>
-    <t>deby_prnmsr512</t>
-  </si>
-  <si>
-    <t>Bismillah prabowo gibran🤲</t>
-  </si>
-  <si>
-    <t>m.sofyan_s.ml</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na banyak gagasan,banyak teori bisanya cuman gelapin uang rakyat itu yng di dukung,memang zaman udh kebalik ya skarang😂</t>
-  </si>
-  <si>
-    <t>dizzyy_mntlng</t>
-  </si>
-  <si>
-    <t>TORANG DG TUAMA🔥🔥</t>
-  </si>
-  <si>
-    <t>dinarwahyu_akunbaru</t>
-  </si>
-  <si>
-    <t>All in🔥</t>
-  </si>
-  <si>
-    <t>adya_llss</t>
-  </si>
-  <si>
-    <t>Bingun sama artis artis mereka padahal rata rata berpendidikan tinggi.. Tapi apa buta mata buta hati banyak dukung paslon yang punya wakil jalur MK dan curang 😢</t>
-  </si>
-  <si>
-    <t>sri_damayanti_022</t>
-  </si>
-  <si>
-    <t>Dikampung aku ka😍seneng bgt bisa ketemu ka Fero langsung😍❤️</t>
-  </si>
-  <si>
-    <t>All in prabowo gibran😍😍😍😍</t>
-  </si>
-  <si>
-    <t>ridwanalvaro_12</t>
-  </si>
-  <si>
-    <t>Keren lu bang 🔥👏</t>
-  </si>
-  <si>
-    <t>vickymci7</t>
-  </si>
-  <si>
-    <t>@fero_walandouw Mantapss 🔥🔥 Terbaik Pak Prabowo 👍😇🙏✌️</t>
-  </si>
-  <si>
-    <t>doddyansyah</t>
-  </si>
-  <si>
-    <t>👏</t>
-  </si>
-  <si>
-    <t>zarhendrik</t>
-  </si>
-  <si>
-    <t>✌🏻✌🏻✌🏻</t>
-  </si>
-  <si>
-    <t>junior_trimunanda</t>
-  </si>
-  <si>
-    <t>ALL IN PRABOWO ✌️🔥</t>
-  </si>
-  <si>
-    <t>aniezaniz2</t>
-  </si>
-  <si>
-    <t>✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️✌️</t>
-  </si>
-  <si>
-    <t>tatimandaaa</t>
-  </si>
-  <si>
-    <t>Makin Mantap Pilih nomer 2 All in Prabowo Loveeeee❤️❤️❤️❤️❤️❤️❤️</t>
-  </si>
-  <si>
-    <t>sulasmita</t>
-  </si>
-  <si>
-    <t>Pak gemoy😍❤️❤️❤️</t>
-  </si>
-  <si>
-    <t>secrettmeong_</t>
-  </si>
-  <si>
-    <t>Yang pendukung @prabowo rata2 kenapa berkelas semua ya❤️</t>
-  </si>
-  <si>
-    <t>askom1805</t>
-  </si>
-  <si>
-    <t>Mantap abang ku✌️💙</t>
-  </si>
-  <si>
-    <t>kevinzethizac</t>
-  </si>
-  <si>
-    <t>maju AMIN !!!🔥</t>
-  </si>
-  <si>
-    <t>miftahul448jannah</t>
-  </si>
-  <si>
-    <t>Kereeen 👌 bang fero</t>
-  </si>
-  <si>
-    <t>sabryan_macca</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na buzzer</t>
-  </si>
-  <si>
-    <t>sam_rajiemin54</t>
-  </si>
-  <si>
-    <t>Pantesan jadi Komisaris😂</t>
-  </si>
-  <si>
-    <t>ajayfalikan</t>
-  </si>
-  <si>
-    <t>Hidup pak Prabowo</t>
-  </si>
-  <si>
-    <t>ghofir04</t>
-  </si>
-  <si>
-    <t>@arya_sam_poer_na gagasannya internet gratis buat mbokep 😂😂😂</t>
-  </si>
-  <si>
-    <t>syarifsyarif4752</t>
-  </si>
-  <si>
-    <t>@see_frzzzzzzz 2kali Prabowo nyapres gak pernah gue milih beliau.. beliau terlalu arogan.. tp setelah diya mau jadi pembantunya Jokowi,,aku malah respect ma pak Wowo.. ternyata setulus tu cintanya kepada Indonesia</t>
-  </si>
-  <si>
-    <t>sriyatun_2375</t>
-  </si>
-  <si>
-    <t>Mantap bang Fero aku mendukung Paslon Abang 👍💪❤️</t>
-  </si>
-  <si>
-    <t>bebyila02</t>
-  </si>
-  <si>
-    <t>@adya_llss itu hak mbak, terserah pilih siapa</t>
-  </si>
-  <si>
-    <t>isnainihayati11</t>
-  </si>
-  <si>
-    <t>Jejak digital .... selamat jadi komisaris😂</t>
-  </si>
-  <si>
-    <t>st_efany8178</t>
-  </si>
-  <si>
-    <t>Prabowo gibran❤️</t>
-  </si>
-  <si>
-    <t>lokeramboncom</t>
-  </si>
-  <si>
-    <t>Jika hanya ada 1 suara di Ambon dalam Pemilihan nanti. Maka itulah Saya Pak @prabowo ✌️</t>
-  </si>
-  <si>
-    <t>poyluccc</t>
-  </si>
-  <si>
-    <t>dapet apa sih??? udh gak laku ya sinetronnya?</t>
+    <t>afti_susanti</t>
+  </si>
+  <si>
+    <t>😂😂jualan goyang doang di tanyakan tak bisa jawab</t>
+  </si>
+  <si>
+    <t>suhadi8750</t>
+  </si>
+  <si>
+    <t>Kita butuh pemimpin yg cerdas muda punya gagasan.bukan yg suka joget joget doang</t>
+  </si>
+  <si>
+    <t>kimcunghuy</t>
+  </si>
+  <si>
+    <t>Kita butuh pemimpin, bukan maskot</t>
+  </si>
+  <si>
+    <t>fero_walandouw</t>
+  </si>
+  <si>
+    <t>@dilah_humaira daripada Jual Agama , gagasan plinplan 😎</t>
+  </si>
+  <si>
+    <t>itsmeardha</t>
+  </si>
+  <si>
+    <t>Gak ngerti gmn konsep kampanye nya ini 🤔</t>
+  </si>
+  <si>
+    <t>riboy_77</t>
+  </si>
+  <si>
+    <t>#asalbukanprabowo</t>
+  </si>
+  <si>
+    <t>lovableempress</t>
+  </si>
+  <si>
+    <t>Pasukan gemoy😍</t>
+  </si>
+  <si>
+    <t>dilah_humaira</t>
+  </si>
+  <si>
+    <t>Jual goyang, kosong gagasan 😂😮</t>
+  </si>
+  <si>
+    <t>rickyalfarizzy__</t>
+  </si>
+  <si>
+    <t>All in Prabowo-Gibran✌🏻🤩🤩</t>
+  </si>
+  <si>
+    <t>karauwanalex</t>
+  </si>
+  <si>
+    <t>All in prabowo🔥🙌</t>
+  </si>
+  <si>
+    <t>@fero_walandouw agama mana yg di jual bro??? Gg kebalik ? Makanya bro jangan banyak goyang nnti otak gg bisa mikir 😂🤪</t>
+  </si>
+  <si>
+    <t>novarizki1311</t>
+  </si>
+  <si>
+    <t>@fero_walandouw wkwkwkw bener bang saya yg muslim aja ngeri sama mulut2 org kampanye bawa2 agama , udah bang fero lanjut memeriahkan kampanye aja komen2 yg kaya gini ga usah di urusin adaaa kami para pendukung 02 pokoknya</t>
+  </si>
+  <si>
+    <t>ingg_el15</t>
+  </si>
+  <si>
+    <t>Sulut "Prabowo-Gibran🤍02🔥</t>
+  </si>
+  <si>
+    <t>didik___harmoko</t>
+  </si>
+  <si>
+    <t>JAWA TIMUR ALL IN PRABOWO  GIBRAN❤️❤️❤️❤️❤️</t>
+  </si>
+  <si>
+    <t>mnhcollection_mujib</t>
+  </si>
+  <si>
+    <t>AMIN ☝☝☝☝☝☝</t>
+  </si>
+  <si>
+    <t>putra_bambu123</t>
+  </si>
+  <si>
+    <t>Guru senam apa??</t>
+  </si>
+  <si>
+    <t>diastutilevi</t>
+  </si>
+  <si>
+    <t>Insya Allah pak Anies presiden RI 2024</t>
+  </si>
+  <si>
+    <t>evanalikendal</t>
+  </si>
+  <si>
+    <t>goyang melulu giliran debat nangis....😂😂😂😂</t>
+  </si>
+  <si>
+    <t>penjuang_anti_warisan</t>
+  </si>
+  <si>
+    <t>Masih zaman ya kampanye joget dan dangdutan gini, ini mah kampanye zaman kuno dan ketinggalan zaman,</t>
+  </si>
+  <si>
+    <t>rizkycand_</t>
+  </si>
+  <si>
+    <t>Rusak Mindset anak muda jika hanya di cekokin dengan goyangan bukan sebuah ide-ide, gagasan, pantesan indonesia turun tingkat literasinya isi nya beginiaan</t>
+  </si>
+  <si>
+    <t>riorizkimahesa</t>
+  </si>
+  <si>
+    <t>ORANG-ORANG yg tanpa Sembako dan Tanpa Kaos akan terus Melonjak secara derastis dan akan memgalahkan Orang2 yg Joget2 dan Mengumpat2. INSYA ALLAH bpk Anies Presiden RI 2024-2029. 🔥</t>
+  </si>
+  <si>
+    <t>arb_aliim232</t>
+  </si>
+  <si>
+    <t>Jogett mulu,, gk da gagasan yaa, modal punya partai dan lnggr kode etik doank,, chuanksss</t>
+  </si>
+  <si>
+    <t>riskauni_</t>
+  </si>
+  <si>
+    <t>Tetap 1</t>
+  </si>
+  <si>
+    <t>lindabadarudin97</t>
+  </si>
+  <si>
+    <t>Anis presiden ❤️</t>
+  </si>
+  <si>
+    <t>uwaisal.qoroni.3386</t>
+  </si>
+  <si>
+    <t>Badut?</t>
+  </si>
+  <si>
+    <t>banatz93</t>
+  </si>
+  <si>
+    <t>Lu prabowo gue follow</t>
+  </si>
+  <si>
+    <t>fauzanqla</t>
+  </si>
+  <si>
+    <t>#asalbukanprabowogibran</t>
+  </si>
+  <si>
+    <t>wida.aryanti.14</t>
+  </si>
+  <si>
+    <t>Salam perubahan AMIN ❤️</t>
+  </si>
+  <si>
+    <t>cameliatan23</t>
+  </si>
+  <si>
+    <t>@afti_susanti mau jualan goyang,jualan combro yg penting gak pake janji dp 0% atau 1 lg gaya nya alay2😂. Tetap no 2 yang paling waras!</t>
+  </si>
+  <si>
+    <t>edhiejhoned</t>
+  </si>
+  <si>
+    <t>Kami butuh gagasan bukan joget... Semakin yakin pilih AMIN</t>
+  </si>
+  <si>
+    <t>kibo3145</t>
+  </si>
+  <si>
+    <t>Prabowo Gibran yessss</t>
+  </si>
+  <si>
+    <t>nblsll</t>
+  </si>
+  <si>
+    <t>@fero_walandouw jngn lngsung ulti bg</t>
+  </si>
+  <si>
+    <t>@_albash_98 abang juga kayanya harus les lagi deh mna yg tdak perlu di publik dn mna yg engg?</t>
+  </si>
+  <si>
+    <t>albasyir_98</t>
+  </si>
+  <si>
+    <t>@afti_susanti bicit banget 😂</t>
+  </si>
+  <si>
+    <t>wakandanomoreindnesiaforever</t>
+  </si>
+  <si>
+    <t>Mana gagasan untuk indonesia emass,, kok joget terusss, masalah di negri ini bxk lohh😂</t>
+  </si>
+  <si>
+    <t>bassam_mee</t>
+  </si>
+  <si>
+    <t>Prabowo yess 😍</t>
+  </si>
+  <si>
+    <t>rafa4lll</t>
+  </si>
+  <si>
+    <t>gak punya prestasi 😂😂</t>
+  </si>
+  <si>
+    <t>husfullaili</t>
+  </si>
+  <si>
+    <t>PRAGIB🔥🔥🔥</t>
+  </si>
+  <si>
+    <t>faiz_abu47</t>
+  </si>
+  <si>
+    <t>Ini konsepnya miLih Pemimpin apa milih biduan gak sih 😂</t>
+  </si>
+  <si>
+    <t>mocha_monalisa</t>
+  </si>
+  <si>
+    <t>Aku padamu abng😍 ALL IN PRABOWO GASSS KEUUNNN🔥</t>
+  </si>
+  <si>
+    <t>waseng_26</t>
+  </si>
+  <si>
+    <t>Waktunya Sulawesi Utara dukung Bapak Prabowo Subianto berdarah Minahasa untuk menjadi Presiden RI🇮🇩 👌✌</t>
+  </si>
+  <si>
+    <t>mhadtea</t>
+  </si>
+  <si>
+    <t>AMIN PRESIDEN 2024 🔥🔥🔥🔥 ---&gt;&gt;&gt;</t>
+  </si>
+  <si>
+    <t>libr.aa30</t>
+  </si>
+  <si>
+    <t>@suhadi8750 ada waktu buat senang" ada waktu buat serius pak busetttt joget juga ga setiap saat🤣🤣🤣 kaya gini juga paslon lain ngikutin tuh</t>
+  </si>
+  <si>
+    <t>ygeminigirl94</t>
+  </si>
+  <si>
+    <t>@itsmeardha belajar, biar ngerti 😝😂😂</t>
+  </si>
+  <si>
+    <t>ndayyy_y</t>
+  </si>
+  <si>
+    <t>@dilah_humaira tapi full bukti nyata😎</t>
+  </si>
+  <si>
+    <t>desiroyani97</t>
+  </si>
+  <si>
+    <t>Anies presiden 2024</t>
+  </si>
+  <si>
+    <t>adi_iqbaal</t>
+  </si>
+  <si>
+    <t>Amin aja dulu❤️😎☝️</t>
+  </si>
+  <si>
+    <t>99.kertas_seiko</t>
+  </si>
+  <si>
+    <t>@fero_walandouw  Waduh jangan langsung di ulti dong bang,😂 Ini pilhan fero klw gk suka tinggl skip, sirik aee nih 01 03, kampanyekan juga noh capres loe mantap bang seridaknya followers loe lihat 02😍</t>
+  </si>
+  <si>
+    <t>abangrafisqi</t>
+  </si>
+  <si>
+    <t>Mana gagasannya, kampanye goyang melulu 😂</t>
+  </si>
+  <si>
+    <t>@afti_susanti gak usah ngegas deh haha</t>
   </si>
   <si>
     <t>sentiment_score</t>
@@ -699,11 +688,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="78.08984375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -714,7 +702,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -725,7 +713,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -736,10 +724,10 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -747,7 +735,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -758,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -769,10 +757,10 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -780,7 +768,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -802,7 +790,7 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -813,32 +801,32 @@
         <v>19</v>
       </c>
       <c r="C10">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -846,10 +834,10 @@
         <v>24</v>
       </c>
       <c r="C13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="232" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -857,7 +845,7 @@
         <v>26</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -879,7 +867,7 @@
         <v>30</v>
       </c>
       <c r="C16">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -890,7 +878,7 @@
         <v>32</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -915,7 +903,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -923,10 +911,10 @@
         <v>38</v>
       </c>
       <c r="C20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -934,7 +922,7 @@
         <v>40</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
@@ -956,7 +944,7 @@
         <v>44</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -967,10 +955,10 @@
         <v>46</v>
       </c>
       <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -978,10 +966,10 @@
         <v>48</v>
       </c>
       <c r="C25">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -989,15 +977,15 @@
         <v>50</v>
       </c>
       <c r="C26">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1005,32 +993,32 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1038,21 +1026,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1060,10 +1048,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1071,7 +1059,7 @@
     </row>
     <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>65</v>
@@ -1088,7 +1076,7 @@
         <v>67</v>
       </c>
       <c r="C35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -1099,7 +1087,7 @@
         <v>69</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -1121,7 +1109,7 @@
         <v>73</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -1132,7 +1120,7 @@
         <v>75</v>
       </c>
       <c r="C39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -1143,7 +1131,7 @@
         <v>77</v>
       </c>
       <c r="C40">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -1154,10 +1142,10 @@
         <v>79</v>
       </c>
       <c r="C41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -1168,7 +1156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -1176,10 +1164,10 @@
         <v>83</v>
       </c>
       <c r="C43">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>84</v>
       </c>
@@ -1187,7 +1175,7 @@
         <v>85</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -1198,7 +1186,7 @@
         <v>87</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -1209,7 +1197,7 @@
         <v>89</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -1220,7 +1208,7 @@
         <v>91</v>
       </c>
       <c r="C47">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -1231,10 +1219,10 @@
         <v>93</v>
       </c>
       <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -1253,7 +1241,18 @@
         <v>97</v>
       </c>
       <c r="C50">
-        <v>-0.5</v>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
